--- a/artfynd/A 15774-2026 artfynd.xlsx
+++ b/artfynd/A 15774-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,63 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38802</v>
+        <v>101663317</v>
       </c>
       <c r="B2" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100117</v>
+        <v>100070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Långbensgroda</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana dalmatina</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bonaparte, 1840</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SV Hagalund, Sm</t>
+          <t>Damm, Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566748.0635677952</v>
+        <v>566803</v>
       </c>
       <c r="R2" t="n">
-        <v>6275215.168920008</v>
+        <v>6275204</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +755,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-05-02</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vildsvinsbökat område med blottad sand</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,70 +790,77 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Lager</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Lydänge</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68161949</v>
+        <v>134020525</v>
       </c>
       <c r="B3" t="n">
-        <v>44578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208306</v>
+        <v>100070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ölvingstorp, Sm</t>
+          <t>Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566785.3302984713</v>
+        <v>566817</v>
       </c>
       <c r="R3" t="n">
-        <v>6275194.848920205</v>
+        <v>6275183</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,29 +882,14 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,37 +898,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Lucia Caroli</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68161948</v>
+        <v>38802</v>
       </c>
       <c r="B4" t="n">
-        <v>44580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,42 +932,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102918</v>
+        <v>100117</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Citronfläckad kärrtrollslända</t>
+          <t>Långbensgroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucorrhinia pectoralis</t>
+          <t>Rana dalmatina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Charpentier, 1825)</t>
+          <t>Bonaparte, 1840</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ölvingstorp, Sm</t>
+          <t>SV Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566785.3302984713</v>
+        <v>566748</v>
       </c>
       <c r="R4" t="n">
-        <v>6275194.848920205</v>
+        <v>6275215</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,29 +989,14 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2006-05-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,31 +1011,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Helena Lager</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>John Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68161950</v>
+        <v>101696288</v>
       </c>
       <c r="B5" t="n">
-        <v>44577</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,39 +1034,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208307</v>
+        <v>101246</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pudrad kärrtrollslända</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucorrhinia albifrons</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Burmeister, 1839)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ölvingstorp, Sm</t>
+          <t>Damm, Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566785.3302984713</v>
+        <v>566803</v>
       </c>
       <c r="R5" t="n">
-        <v>6275194.848920205</v>
+        <v>6275204</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,29 +1105,29 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Brummade förbi på 10 m höjd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,31 +1142,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>John Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68161946</v>
+        <v>101696301</v>
       </c>
       <c r="B6" t="n">
-        <v>4348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,16 +1165,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102232</v>
+        <v>102118</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bredkantad dykare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dytiscus latissimus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1203,22 +1182,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ölvingstorp, Sm</t>
+          <t>Damm, Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566785.3302984713</v>
+        <v>566803</v>
       </c>
       <c r="R6" t="n">
-        <v>6275194.848920205</v>
+        <v>6275204</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,29 +1228,24 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-08</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,31 +1260,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>John Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68161951</v>
+        <v>101696310</v>
       </c>
       <c r="B7" t="n">
-        <v>44542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,39 +1283,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102920</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön mosaikslända</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Aeshna viridis</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Eversmann, 1836</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ölvingstorp, Sm</t>
+          <t>Damm, Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566785.3302984713</v>
+        <v>566803</v>
       </c>
       <c r="R7" t="n">
-        <v>6275194.848920205</v>
+        <v>6275204</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1369,29 +1346,14 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,31 +1368,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>John Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68161947</v>
+        <v>101911943</v>
       </c>
       <c r="B8" t="n">
-        <v>4334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,42 +1391,56 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102249</v>
+        <v>102918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bred paljettdykare</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphoderus bilineatus</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(De Geer, 1774)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Charpentier, 1825)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ölvingstorp, Sm</t>
+          <t>Hagalund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566785.3302984713</v>
+        <v>566771</v>
       </c>
       <c r="R8" t="n">
-        <v>6275194.848920205</v>
+        <v>6275189</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,29 +1462,24 @@
           <t>Ljungby</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-06-06</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-06-08</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,12 +1494,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>John Persson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1548,68 +1510,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101663317</v>
+        <v>114546005</v>
       </c>
       <c r="B9" t="n">
-        <v>55599</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100070</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Damm, Hagalund, Sm</t>
+          <t>Ölvingstorp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566803.3652081982</v>
+        <v>566681</v>
       </c>
       <c r="R9" t="n">
-        <v>6275205.040212791</v>
+        <v>6275070</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1633,27 +1575,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Vildsvinsbökat område med blottad sand</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,27 +1595,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101696288</v>
+        <v>114546008</v>
       </c>
       <c r="B10" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,56 +1618,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101246</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Damm, Hagalund, Sm</t>
+          <t>Ölvingstorp, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566803.3652081982</v>
+        <v>566666</v>
       </c>
       <c r="R10" t="n">
-        <v>6275205.040212791</v>
+        <v>6275119</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1769,27 +1672,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>22:15</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>22:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Brummade förbi på 10 m höjd</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1804,27 +1692,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101911939</v>
+        <v>114546009</v>
       </c>
       <c r="B11" t="n">
-        <v>4348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,47 +1715,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102232</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bredkantad dykare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dytiscus latissimus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>fälla</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hagalund, Sm</t>
+          <t>Ölvingstorp, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566771.6269815366</v>
+        <v>566658</v>
       </c>
       <c r="R11" t="n">
-        <v>6275189.678983573</v>
+        <v>6275107</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1896,22 +1769,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1926,31 +1789,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101911940</v>
+        <v>114546012</v>
       </c>
       <c r="B12" t="n">
-        <v>44577</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,47 +1812,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208307</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pudrad kärrtrollslända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucorrhinia albifrons</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Burmeister, 1839)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hagalund, Sm</t>
+          <t>Ölvingstorp, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566771.6269815366</v>
+        <v>566668</v>
       </c>
       <c r="R12" t="n">
-        <v>6275189.678983573</v>
+        <v>6275102</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,22 +1866,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,31 +1886,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101911941</v>
+        <v>114546013</v>
       </c>
       <c r="B13" t="n">
-        <v>44578</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,47 +1909,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208306</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hagalund, Sm</t>
+          <t>Ölvingstorp, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566771.6269815366</v>
+        <v>566667</v>
       </c>
       <c r="R13" t="n">
-        <v>6275189.678983573</v>
+        <v>6275102</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2148,22 +1963,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,31 +1983,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101911938</v>
+        <v>121237336</v>
       </c>
       <c r="B14" t="n">
-        <v>4334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,47 +2006,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102249</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bred paljettdykare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Graphoderus bilineatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(De Geer, 1774)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>fälla</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hagalund, Sm</t>
+          <t>Ölvingstorp 31:1, 225 m V-VSV Hagalunds växthus, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566771.6269815366</v>
+        <v>566604</v>
       </c>
       <c r="R14" t="n">
-        <v>6275189.678983573</v>
+        <v>6275104</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2274,22 +2060,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,775 +2076,24 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>i gräns mellan granblandskog och tallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Tomas Burén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>101911943</v>
-      </c>
-      <c r="B15" t="n">
-        <v>44580</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>102918</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Citronfläckad kärrtrollslända</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Leucorrhinia pectoralis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Charpentier, 1825)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Hagalund, Sm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>566771.6269815366</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6275189.678983573</v>
-      </c>
-      <c r="S15" t="n">
-        <v>20</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>114546005</v>
-      </c>
-      <c r="B16" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ölvingstorp, Sm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>566681</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6275070</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>114546009</v>
-      </c>
-      <c r="B17" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ölvingstorp, Sm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>566658</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6275107</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>114546008</v>
-      </c>
-      <c r="B18" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ölvingstorp, Sm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>566666</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6275119</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>114546013</v>
-      </c>
-      <c r="B19" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Ölvingstorp, Sm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>566667</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6275102</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>114546012</v>
-      </c>
-      <c r="B20" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Ölvingstorp, Sm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>566668</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6275102</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-11-16</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Samuel Persson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>121237336</v>
-      </c>
-      <c r="B21" t="n">
-        <v>100371</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Ölvingstorp 31:1, 225 m V-VSV Hagalunds växthus, Sm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>566604</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6275104</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>i gräns mellan granblandskog och tallskog</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
           <t>Tomas Burén</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Tomas Burén</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15774-2026 artfynd.xlsx
+++ b/artfynd/A 15774-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101663317</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020525</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/38802</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101696288</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101696301</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101696310</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1507,6 +1542,11 @@
           <t>Trollsländor, vattenlevande skalbaggar och blodigel</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101911943</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1604,6 +1644,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114546005</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114546008</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1798,6 +1848,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114546009</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114546012</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114546013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2094,8 +2159,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121237336</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>